--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488026_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488026_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4154</v>
+        <v>6.7491</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5733</v>
+        <v>6.8789</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1579</v>
+        <v>-0.1298</v>
       </c>
       <c r="G2" t="n">
         <v>6.1492</v>
@@ -610,13 +610,13 @@
         <v>1.1893</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3374</v>
+        <v>-0.0037</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2423</v>
+        <v>0.548</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5797</v>
+        <v>-0.5517</v>
       </c>
       <c r="V2" t="n">
         <v>0.6036</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5938</v>
+        <v>3.5729</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9621</v>
+        <v>3.1658</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6317</v>
+        <v>0.4071</v>
       </c>
       <c r="G3" t="n">
         <v>3.204</v>
@@ -688,13 +688,13 @@
         <v>1.3876</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1915</v>
+        <v>0.1706</v>
       </c>
       <c r="T3" t="n">
-        <v>0.18</v>
+        <v>0.3837</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0116</v>
+        <v>-0.213</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4271</v>
+        <v>2.1473</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5204</v>
+        <v>3.4372</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0933</v>
+        <v>-1.2899</v>
       </c>
       <c r="G4" t="n">
         <v>-0.9903</v>
@@ -766,13 +766,13 @@
         <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9791</v>
+        <v>-0.2588</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8736</v>
+        <v>0.0433</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1055</v>
+        <v>-0.3021</v>
       </c>
       <c r="V4" t="n">
         <v>1.8107</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GUZMAN SALINAS</t>
+          <t>E. DOMENECH ANTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7907</v>
+        <v>1.9416</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9236</v>
+        <v>2.3688</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.133</v>
+        <v>-0.4272</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3992</v>
+        <v>0.8514</v>
       </c>
       <c r="H5" t="n">
-        <v>0.655</v>
+        <v>-2.0069</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0542</v>
+        <v>2.8583</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2068</v>
+        <v>2.9554</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9976</v>
+        <v>-0.6722</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2092</v>
+        <v>3.6277</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.606</v>
+        <v>-2.1041</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3426</v>
+        <v>-1.3347</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.2634</v>
+        <v>-0.7693</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3964</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>-2.1805</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4137</v>
+        <v>-0.1257</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4992</v>
+        <v>0.4571</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08550000000000001</v>
+        <v>-0.5829</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2071</v>
+        <v>1.8107</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2071</v>
+        <v>1.1367</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. DOMENECH ANTE</t>
+          <t>A. GUZMAN SALINAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7264</v>
+        <v>1.0016</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3501</v>
+        <v>3.3311</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6237</v>
+        <v>-2.3295</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8514</v>
+        <v>-0.3992</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.0069</v>
+        <v>0.655</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8583</v>
+        <v>-1.0542</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9554</v>
+        <v>3.2068</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6722</v>
+        <v>1.9976</v>
       </c>
       <c r="L6" t="n">
-        <v>3.6277</v>
+        <v>1.2092</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1041</v>
+        <v>-3.606</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3347</v>
+        <v>-1.3426</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7693</v>
+        <v>-2.2634</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1805</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.341</v>
+        <v>-0.2028</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5616</v>
+        <v>-0.0917</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7794</v>
+        <v>-0.1111</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8107</v>
+        <v>1.2071</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1367</v>
+        <v>1.2071</v>
       </c>
       <c r="X6" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. KOROL</t>
+          <t>P. BALLESTER MANQUE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6999</v>
+        <v>0.5924</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6789</v>
+        <v>0.2384</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.979</v>
+        <v>0.354</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4872</v>
+        <v>-0.1723</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8774999999999999</v>
+        <v>-0.3081</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.3648</v>
+        <v>0.1358</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7829</v>
+        <v>0.3632</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4219</v>
+        <v>0.3632</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.639</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.2702</v>
+        <v>-0.5355</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5443</v>
+        <v>-0.6713</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7258</v>
+        <v>0.1358</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4538</v>
+        <v>-0.167</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4134</v>
+        <v>-0.1248</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0403</v>
+        <v>-0.0422</v>
       </c>
       <c r="V7" t="n">
         <v>0.337</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1367</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. BALLESTER MANQUE</t>
+          <t>N. KOROL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5362</v>
+        <v>-0.3188</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2384</v>
+        <v>2.6602</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2978</v>
+        <v>-2.979</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1723</v>
+        <v>-1.4872</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3081</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1358</v>
+        <v>-2.3648</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3632</v>
+        <v>1.7829</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3632</v>
+        <v>2.4219</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.639</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5355</v>
+        <v>-3.2702</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6713</v>
+        <v>-1.5443</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1358</v>
+        <v>-1.7258</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5947</v>
+        <v>1.3876</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2232</v>
+        <v>0.4351</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1248</v>
+        <v>0.3947</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0984</v>
+        <v>0.0403</v>
       </c>
       <c r="V8" t="n">
         <v>0.337</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X8" t="n">
-        <v>0.337</v>
+        <v>-1.1367</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6543</v>
+        <v>-4.5232</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6745</v>
+        <v>-3.7119</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9798</v>
+        <v>-0.8113</v>
       </c>
       <c r="G9" t="n">
         <v>-3.0192</v>
@@ -1156,13 +1156,13 @@
         <v>1.1893</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2966</v>
+        <v>0.4276</v>
       </c>
       <c r="T9" t="n">
-        <v>2.9589</v>
+        <v>0.9215</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6623</v>
+        <v>-0.4938</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9405</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. CUBERO ROJANO</t>
+          <t>C. ZULUAGA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9384</v>
+        <v>-4.6706</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3651</v>
+        <v>-2.4573</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.5733</v>
+        <v>-2.2133</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.767</v>
+        <v>-2.3428</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3066</v>
+        <v>-1.5374</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4604</v>
+        <v>-0.8054</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4372</v>
+        <v>-0.3439</v>
       </c>
       <c r="K10" t="n">
-        <v>1.036</v>
+        <v>-0.1949</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5988</v>
+        <v>-0.149</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.2042</v>
+        <v>-1.9989</v>
       </c>
       <c r="N10" t="n">
         <v>-1.3426</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8617</v>
+        <v>-0.6563</v>
       </c>
       <c r="P10" t="n">
         <v>-0.7929</v>
@@ -1234,28 +1234,28 @@
         <v>1.1893</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1714</v>
+        <v>-0.3983</v>
       </c>
       <c r="T10" t="n">
-        <v>0.18</v>
+        <v>-0.1312</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3513</v>
+        <v>-0.2671</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2071</v>
+        <v>-1.1367</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2071</v>
+        <v>-1.1367</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. ZULUAGA</t>
+          <t>R. CUBERO ROJANO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0605</v>
+        <v>-4.956</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7629</v>
+        <v>-1.467</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2976</v>
+        <v>-3.4891</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3428</v>
+        <v>-2.767</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5374</v>
+        <v>-0.3066</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8054</v>
+        <v>-2.4604</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3439</v>
+        <v>0.4372</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1949</v>
+        <v>1.036</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.149</v>
+        <v>-0.5988</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9989</v>
+        <v>-3.2042</v>
       </c>
       <c r="N11" t="n">
         <v>-1.3426</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6563</v>
+        <v>-1.8617</v>
       </c>
       <c r="P11" t="n">
         <v>-0.7929</v>
@@ -1312,22 +1312,22 @@
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7881</v>
+        <v>-0.189</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4368</v>
+        <v>0.0781</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3513</v>
+        <v>-0.2671</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1367</v>
+        <v>-1.2071</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1367</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="12">
@@ -1348,10 +1348,10 @@
         <v>1.5363</v>
       </c>
       <c r="E12" t="n">
-        <v>14.4443</v>
+        <v>14.4442</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.9081</v>
+        <v>-12.908</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9733999999999989</v>
@@ -1390,19 +1390,19 @@
         <v>12.8845</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3119999999999996</v>
+        <v>-0.3119999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4786</v>
+        <v>2.4787</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.790500000000001</v>
+        <v>-2.7907</v>
       </c>
       <c r="V12" t="n">
-        <v>2.821800000000001</v>
+        <v>2.821799999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>7.298000000000001</v>
+        <v>7.298</v>
       </c>
       <c r="X12" t="n">
         <v>-4.4764</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.194</v>
+        <v>4.14</v>
       </c>
       <c r="E13" t="n">
-        <v>7.0614</v>
+        <v>5.839</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8674</v>
+        <v>-1.699</v>
       </c>
       <c r="G13" t="n">
         <v>3.739</v>
@@ -1468,13 +1468,13 @@
         <v>1.784</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4816</v>
+        <v>0.4276</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2797</v>
+        <v>1.0573</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7981</v>
+        <v>-0.6297</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8107</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4456</v>
+        <v>2.5756</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5446</v>
+        <v>2.6465</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.099</v>
+        <v>-0.0709</v>
       </c>
       <c r="G14" t="n">
         <v>1.0928</v>
@@ -1546,13 +1546,13 @@
         <v>1.3876</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3528</v>
+        <v>0.4827</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1176</v>
+        <v>0.2194</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2352</v>
+        <v>0.2633</v>
       </c>
       <c r="V14" t="n">
         <v>0.6036</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.704</v>
+        <v>0.6655</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7261</v>
+        <v>1.8279</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0221</v>
+        <v>-1.1625</v>
       </c>
       <c r="G15" t="n">
         <v>0.6849</v>
@@ -1624,13 +1624,13 @@
         <v>1.5858</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1377</v>
+        <v>-0.1762</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2423</v>
+        <v>0.3442</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3801</v>
+        <v>-0.5205</v>
       </c>
       <c r="V15" t="n">
         <v>0.5532</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VICENTE BOSCH</t>
+          <t>M. GAMEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3304</v>
+        <v>0.4046</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5024</v>
+        <v>3.6253</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1719</v>
+        <v>-3.2207</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.7216</v>
+        <v>1.7631</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3996</v>
+        <v>-0.0394</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.322</v>
+        <v>1.8026</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1887</v>
+        <v>4.4879</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0089</v>
+        <v>1.0896</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.1975</v>
+        <v>3.3983</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5329</v>
+        <v>-2.7247</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4085</v>
+        <v>-1.129</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1244</v>
+        <v>-1.5957</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9911</v>
+        <v>0.5947</v>
       </c>
       <c r="Q16" t="n">
+        <v>-0.9911</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.5858</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.3588</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.1286</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.4874</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-1.5944</v>
+      </c>
+      <c r="W16" t="n">
         <v>0</v>
       </c>
-      <c r="R16" t="n">
-        <v>0.9911</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.7943</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.5543</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.2666</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.1367</v>
-      </c>
       <c r="X16" t="n">
-        <v>-0.8701</v>
+        <v>-1.5944</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. GAMEZ SANCHEZ</t>
+          <t>J. VICENTE BOSCH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6069</v>
+        <v>0.0601</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8104</v>
+        <v>1.4005</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.4172</v>
+        <v>-1.3404</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7631</v>
+        <v>-1.7216</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0394</v>
+        <v>-0.3996</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8026</v>
+        <v>-1.322</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4879</v>
+        <v>-0.1887</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0896</v>
+        <v>1.0089</v>
       </c>
       <c r="L17" t="n">
-        <v>3.3983</v>
+        <v>-1.1975</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.7247</v>
+        <v>-1.5329</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.129</v>
+        <v>-1.4085</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5957</v>
+        <v>-0.1244</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5858</v>
+        <v>0.9911</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3703</v>
+        <v>0.524</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6864</v>
+        <v>0.4525</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6839</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5944</v>
+        <v>0.2666</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1367</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5944</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.688</v>
+        <v>-1.5372</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0565</v>
+        <v>-0.1584</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6315</v>
+        <v>-1.3788</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1831</v>
@@ -1858,13 +1858,13 @@
         <v>1.3876</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7895</v>
+        <v>-0.6387</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0072</v>
+        <v>-0.1091</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7823</v>
+        <v>-0.5296</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1207</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. PALOMARES CALDERON</t>
+          <t>F. CHEKRI KOURAYCHE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4424</v>
+        <v>-3.9697</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2429</v>
+        <v>-2.2024</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.1995</v>
+        <v>-1.7673</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1831</v>
+        <v>-1.7496</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9469</v>
+        <v>-0.4813</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.13</v>
+        <v>-1.2683</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8086</v>
+        <v>0.4432</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4844</v>
+        <v>1.191</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.6758</v>
+        <v>-0.7478</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.9917</v>
+        <v>-2.1928</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.5375</v>
+        <v>-1.6723</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4542</v>
+        <v>-0.5205</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.7751</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.9556</v>
+        <v>-1.9822</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1805</v>
+        <v>0.9911</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1034</v>
+        <v>-0.0973</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1638</v>
+        <v>-0.256</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0604</v>
+        <v>0.1587</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4124</v>
+        <v>-1.1316</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7403</v>
+        <v>-0.4074</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3278</v>
+        <v>-0.7243000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. CHEKRI KOURAYCHE</t>
+          <t>C. PALOMARES CALDERON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.1536</v>
+        <v>-4.3448</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.508</v>
+        <v>-0.7523</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6456</v>
+        <v>-3.5926</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7496</v>
+        <v>-2.1831</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4813</v>
+        <v>0.9469</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2683</v>
+        <v>-3.13</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4432</v>
+        <v>1.8086</v>
       </c>
       <c r="K20" t="n">
-        <v>1.191</v>
+        <v>3.4844</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7478</v>
+        <v>-1.6758</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1928</v>
+        <v>-3.9917</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6723</v>
+        <v>-2.5375</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5205</v>
+        <v>-1.4542</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9911</v>
+        <v>-2.7751</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>-4.9556</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9911</v>
+        <v>2.1805</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2812</v>
+        <v>0.201</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5616</v>
+        <v>0.6545</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2803</v>
+        <v>-0.4535</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1316</v>
+        <v>0.4124</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.4074</v>
+        <v>1.7403</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-1.3278</v>
       </c>
     </row>
     <row r="21">
@@ -2047,19 +2047,19 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.216900000000001</v>
+        <v>-2.0059</v>
       </c>
       <c r="E21" t="n">
-        <v>12.8375</v>
+        <v>12.2261</v>
       </c>
       <c r="F21" t="n">
-        <v>-14.0542</v>
+        <v>-14.2322</v>
       </c>
       <c r="G21" t="n">
         <v>1.442399999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5458000000000001</v>
+        <v>-0.5458000000000003</v>
       </c>
       <c r="I21" t="n">
         <v>1.9884</v>
@@ -2071,7 +2071,7 @@
         <v>11.1871</v>
       </c>
       <c r="L21" t="n">
-        <v>6.956099999999999</v>
+        <v>6.956100000000001</v>
       </c>
       <c r="M21" t="n">
         <v>-16.7003</v>
@@ -2092,13 +2092,13 @@
         <v>11.8935</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1534</v>
+        <v>0.3643</v>
       </c>
       <c r="T21" t="n">
-        <v>3.1025</v>
+        <v>2.4914</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.9493</v>
+        <v>-2.1272</v>
       </c>
       <c r="V21" t="n">
         <v>-2.8216</v>
